--- a/event_planner_forms/003_ticket_printing_quantity_request_form--event_planner_forms.xlsx
+++ b/event_planner_forms/003_ticket_printing_quantity_request_form--event_planner_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>print_run</t>
+          <t>print_run_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Print Run</t>
+          <t>Print Run 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ticket Type Other</t>
+          <t>Ticket Type Other Value</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Submitted by</t>
+          <t>Submitted By Value</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Print Method</t>
+          <t>Print Method Other</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>print_method</t>
+          <t>print_method_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Print Method</t>
+          <t>Print Method 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>submitted_by</t>
+          <t>submitted_by_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Submitted by</t>
+          <t>Submitted By 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1101,7 +1101,7 @@
   <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1216,63 +1216,63 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>print_run_choices</t>
+          <t>print_run_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>print_run_choices</t>
+          <t>print_run_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>print_run_choices</t>
+          <t>print_run_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>print_method_choices</t>
+          <t>print_method_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1381,7 +1381,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>print_method_choices</t>
+          <t>print_method_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1398,7 +1398,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>submitted_by_choices</t>
+          <t>submitted_by_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1415,7 +1415,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>submitted_by_choices</t>
+          <t>submitted_by_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1432,7 +1432,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>submitted_by_choices</t>
+          <t>submitted_by_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
